--- a/relatorio_grupos_datasets.xlsx
+++ b/relatorio_grupos_datasets.xlsx
@@ -535,17 +535,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Misto (Dominante: Powertrain &amp; Motor (RPM, Torque, Potencia))</t>
+          <t>Misto (Dominante: Navegacao, Rota &amp; Elevacao (GPS))</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Powertrain &amp; Motor (RPM, Torque, Potencia) | Transmissao &amp; Troca de Marchas | Frenagem &amp; Pedais | Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Dinamica Lateral &amp; Curvas (IMU / Giroscopio) | Consumo de Combustivel &amp; Gases | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS) | Gestao de Frota &amp; Viagens (Trip Logs)</t>
+          <t>Powertrain &amp; Motor (RPM, Torque, Potencia) | Frenagem &amp; Pedais | Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Dinamica Lateral &amp; Curvas (IMU / Giroscopio) | Consumo de Combustivel &amp; Gases | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS)</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Conjunto estruturado em pasta reunindo 21 arquivo(s) (totalizando 879.39 MB) e 155 variavel(is) unicas. O perfil dos dados abrange: monitoramento de performance de motor e combustao (RPM, torque, carga); escalonamento e selecao de marchas; dinamica de desaceleracao e acionamento de pedais; series temporais de velocidade do veiculo e aceleracao longitudinal; medicoes da IMU (aceleracoes laterais, giroscopio e angulo de estercamento/slip); taxa de consumo de combustivel e emissao de efluentes; parametros eletricos de alta voltagem, estado de carga (SOC) e corrente; posicionamento geografico via GPS, altitudes, rumo (heading) e trajetorias; historico de viagens (trips), status operacionais e IDs de acompanhamento. Exemplo de atributos mapeados: [SCS_Error, SCS_Coding, GBX_Precontrol_Torque, BoostPressure, ENG_Trq_ZWR, GBX_Coding_MSG, SCS_Tip_Restart, WIV_Sensorerror].</t>
+          <t>Conjunto estruturado em pasta reunindo 21 arquivo(s) (totalizando 879.39 MB) e 155 variavel(is) unicas. Temas detectados, com as colunas que os originaram: Powertrain &amp; Motor (RPM, Torque, Potencia) (colunas: ENG_Trq_DMD, ENG_Trq_ZWR, ENG_Trq_m_ex, EngineSpeed_CAN, GBX_Precontrol_Torque); Frenagem &amp; Pedais (colunas: AccPedal); Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: VehicleSpeed); Dinamica Lateral &amp; Curvas (IMU / Giroscopio) (colunas: Latitude_IMU, Longitude_IMU, Time_IMU, G_force, Gyroscope_X); Consumo de Combustivel &amp; Gases (colunas: FuelConsumption); Bateria &amp; Sistema Eletrico (EV / Hibrido) (colunas: Current sec); Navegacao, Rota &amp; Elevacao (GPS) (colunas: Direction, Distance, GPS fix quality, Latitude, Longitude). Amostra de colunas (ordem de leitura): [AI 1, ASR, AccPedal, AirCondition, AirIntakeTemperature, AmbientTemperature, BoostPressure, BrkVoltage].</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (0.02 MB) estruturado com 7 colunas/variaveis. Contem registros focados em: escalonamento e selecao de marchas; especificacoes estaticas de engenharia (peso, classe do veiculo, tipo de motor e tracao). Amostra de colunas presentes: [Transmission, Drive Wheels, VehId, Engine Configuration &amp; Displacement, Vehicle Type, Generalized_Weight, Vehicle Class].</t>
+          <t>Arquivo de dados individual (0.02 MB) estruturado com 7 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: VehId, Generalized_Weight). Amostra de colunas (ordem de leitura): [VehId, Vehicle Type, Vehicle Class, Engine Configuration &amp; Displacement, Transmission, Drive Wheels, Generalized_Weight].</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (0.01 MB) estruturado com 7 colunas/variaveis. Contem registros focados em: escalonamento e selecao de marchas; especificacoes estaticas de engenharia (peso, classe do veiculo, tipo de motor e tracao). Amostra de colunas presentes: [Transmission, EngineType, Drive Wheels, VehId, Engine Configuration &amp; Displacement, Generalized_Weight, Vehicle Class].</t>
+          <t>Arquivo de dados individual (0.01 MB) estruturado com 7 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: VehId, Generalized_Weight). Amostra de colunas (ordem de leitura): [VehId, EngineType, Vehicle Class, Engine Configuration &amp; Displacement, Transmission, Drive Wheels, Generalized_Weight].</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (0.00 MB) estruturado com 5 colunas/variaveis. Contem registros focados em: historico de viagens (trips), status operacionais e IDs de acompanhamento; especificacoes estaticas de engenharia (peso, classe do veiculo, tipo de motor e tracao). Amostra de colunas presentes: [fleet_test_id, axle_class, vehicle_id, total_mass_with_trailer, gross_vehicle_weight].</t>
+          <t>Arquivo de dados individual (0.00 MB) estruturado com 5 colunas/variaveis. Temas detectados, com as colunas que os originaram: Gestao de Frota &amp; Viagens (Trip Logs) (colunas: fleet_test_id); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id, gross_vehicle_weight). Amostra de colunas (ordem de leitura): [vehicle_id, fleet_test_id, gross_vehicle_weight, total_mass_with_trailer, axle_class].</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Conjunto estruturado em pasta reunindo 1 arquivo(s) (totalizando 0.17 MB) e 3 variavel(is) unicas. O perfil dos dados abrange: series temporais de velocidade do veiculo e aceleracao longitudinal. Exemplo de atributos mapeados: [speed, epoch, hdop].</t>
+          <t>Conjunto estruturado em pasta reunindo 1 arquivo(s) (totalizando 0.17 MB) e 3 variavel(is) unicas. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: speed). Amostra de colunas (ordem de leitura): [epoch, speed, hdop].</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Consumo de Combustivel &amp; Gases | Navegacao, Rota &amp; Elevacao (GPS) | Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Navegacao, Rota &amp; Elevacao (GPS) | Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (15.62 MB) estruturado com 19 colunas/variaveis. Contem registros focados em: series temporais de velocidade do veiculo e aceleracao longitudinal; taxa de consumo de combustivel e emissao de efluentes; posicionamento geografico via GPS, altitudes, rumo (heading) e trajetorias; historico de viagens (trips), status operacionais e IDs de acompanhamento; especificacoes estaticas de engenharia (peso, classe do veiculo, tipo de motor e tracao). Amostra de colunas presentes: [n_signal_loss, distance, home_base, track_gap, max_speed, avg_hdop, service_area_fuel, tour_id].</t>
+          <t>Arquivo de dados individual (15.62 MB) estruturado com 19 colunas/variaveis. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: avg_speed, max_speed); Navegacao, Rota &amp; Elevacao (GPS) (colunas: track_id, distance, track_gap); Gestao de Frota &amp; Viagens (Trip Logs) (colunas: start_time); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id). Amostra de colunas (ordem de leitura): [track_id, vehicle_id, tour_id, start_time, stop_time, distance, track_gap, avg_speed].</t>
         </is>
       </c>
     </row>

--- a/relatorio_grupos_datasets.xlsx
+++ b/relatorio_grupos_datasets.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -516,79 +516,79 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aegis</t>
+          <t>2013-1.csv</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pasta / Grupo</t>
+          <t>Arquivo (CSV)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>879.39</v>
+        <v>0.21</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Misto (Dominante: Navegacao, Rota &amp; Elevacao (GPS))</t>
+          <t>Gestao de Frota &amp; Viagens (Trip Logs)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Powertrain &amp; Motor (RPM, Torque, Potencia) | Frenagem &amp; Pedais | Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Dinamica Lateral &amp; Curvas (IMU / Giroscopio) | Consumo de Combustivel &amp; Gases | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS)</t>
+          <t>Gestao de Frota &amp; Viagens (Trip Logs)</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Conjunto estruturado em pasta reunindo 21 arquivo(s) (totalizando 879.39 MB) e 155 variavel(is) unicas. Temas detectados, com as colunas que os originaram: Powertrain &amp; Motor (RPM, Torque, Potencia) (colunas: ENG_Trq_DMD, ENG_Trq_ZWR, ENG_Trq_m_ex, EngineSpeed_CAN, GBX_Precontrol_Torque); Frenagem &amp; Pedais (colunas: AccPedal); Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: VehicleSpeed); Dinamica Lateral &amp; Curvas (IMU / Giroscopio) (colunas: Latitude_IMU, Longitude_IMU, Time_IMU, G_force, Gyroscope_X); Consumo de Combustivel &amp; Gases (colunas: FuelConsumption); Bateria &amp; Sistema Eletrico (EV / Hibrido) (colunas: Current sec); Navegacao, Rota &amp; Elevacao (GPS) (colunas: Direction, Distance, GPS fix quality, Latitude, Longitude). Amostra de colunas (ordem de leitura): [AI 1, ASR, AccPedal, AirCondition, AirIntakeTemperature, AmbientTemperature, BoostPressure, BrkVoltage].</t>
+          <t>Arquivo de dados individual (0.21 MB) estruturado com 11 colunas/variaveis. Temas detectados, com as colunas que os originaram: Gestao de Frota &amp; Viagens (Trip Logs) (colunas: Fleet). Amostra de colunas (ordem de leitura): [ExtractDate, OrganisationURI, OrganisationLabel, ServiceTypeURI, ServiceTypeLabel, Fleet, Vehicle, Fuel].</t>
         </is>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VED_Static_Data_ICE&amp;HEV.xlsx</t>
+          <t>Aegis</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Arquivo (XLSX)</t>
+          <t>Pasta / Grupo</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Misto (Dominante: Perfil de Veiculo &amp; Especificacoes Tecnicas)</t>
+          <t>Sem colunas / Erro</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Transmissao &amp; Troca de Marchas | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (0.02 MB) estruturado com 7 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: VehId, Generalized_Weight). Amostra de colunas (ordem de leitura): [VehId, Vehicle Type, Vehicle Class, Engine Configuration &amp; Displacement, Transmission, Drive Wheels, Generalized_Weight].</t>
+          <t>Conjunto estruturado em pasta reunindo 21 arquivo(s) (totalizando 0.00 MB) e 0 variavel(is) unicas. Temas detectados, com as colunas que os originaram: atributos gerais de dados nao diretamente mapeados no dicionario padrao. Amostra de colunas (ordem de leitura): [Nenhuma coluna identificada].</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VED_Static_Data_PHEV&amp;EV.xlsx</t>
+          <t>CONSOLIDADO COMBUSTVEL-Controladoria.xlsx</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -600,130 +600,562 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.01</v>
+        <v>19.75</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Misto (Dominante: Perfil de Veiculo &amp; Especificacoes Tecnicas)</t>
+          <t>Nao identificado / Outros</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Transmissao &amp; Troca de Marchas | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (0.01 MB) estruturado com 7 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: VehId, Generalized_Weight). Amostra de colunas (ordem de leitura): [VehId, EngineType, Vehicle Class, Engine Configuration &amp; Displacement, Transmission, Drive Wheels, Generalized_Weight].</t>
+          <t>Arquivo de dados individual (19.75 MB) estruturado com 13 colunas/variaveis. Temas detectados, com as colunas que os originaram: atributos gerais de dados nao diretamente mapeados no dicionario padrao. Amostra de colunas (ordem de leitura): [Equipamento, Motorista, Descrição, Modelo, Marca/Tipo, Ano, Tipo Veículo, Litros].</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>fleet.csv</t>
+          <t>DimensionTables.xlsx</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Arquivo (CSV)</t>
+          <t>Arquivo (XLSX)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Misto (Dominante: Perfil de Veiculo &amp; Especificacoes Tecnicas)</t>
+          <t>Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+          <t>Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Arquivo de dados individual (0.00 MB) estruturado com 5 colunas/variaveis. Temas detectados, com as colunas que os originaram: Gestao de Frota &amp; Viagens (Trip Logs) (colunas: fleet_test_id); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id, gross_vehicle_weight). Amostra de colunas (ordem de leitura): [vehicle_id, fleet_test_id, gross_vehicle_weight, total_mass_with_trailer, axle_class].</t>
+          <t>Arquivo de dados individual (1.14 MB) estruturado com 2 colunas/variaveis. Temas detectados, com as colunas que os originaram: Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: Driver ID, Driver). Amostra de colunas (ordem de leitura): [Driver ID, Driver].</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>EV_Predictive_Maintenance_Dataset_15min.csv</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Pasta / Grupo</t>
+          <t>Arquivo (CSV)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.17</v>
+        <v>88.59</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X)</t>
+          <t>Misto (Dominante: Bateria &amp; Sistema Eletrico (EV / Hibrido))</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X)</t>
+          <t>Powertrain &amp; Motor (RPM, Torque, Potencia) | Frenagem &amp; Pedais | Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Conjunto estruturado em pasta reunindo 1 arquivo(s) (totalizando 0.17 MB) e 3 variavel(is) unicas. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: speed). Amostra de colunas (ordem de leitura): [epoch, speed, hdop].</t>
+          <t>Arquivo de dados individual (88.59 MB) estruturado com 30 colunas/variaveis. Temas detectados, com as colunas que os originaram: Powertrain &amp; Motor (RPM, Torque, Potencia) (colunas: Motor_Torque, Motor_RPM); Frenagem &amp; Pedais (colunas: Brake_Pad_Wear, Brake_Pressure, Reg_Brake_Efficiency); Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: Driving_Speed); Bateria &amp; Sistema Eletrico (EV / Hibrido) (colunas: SoC, Battery_Voltage, Battery_Current, Battery_Temperature, Power_Consumption); Navegacao, Rota &amp; Elevacao (GPS) (colunas: Distance_Traveled, Route_Roughness); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: Load_Weight). Amostra de colunas (ordem de leitura): [Timestamp, SoC, SoH, Battery_Voltage, Battery_Current, Battery_Temperature, Charge_Cycles, Motor_Temperature].</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Fleet_Maintenance_Analytics_Dataset.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (XLSX)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Nao identificado / Outros</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Nenhum</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (0.21 MB) estruturado com 16 colunas/variaveis. Temas detectados, com as colunas que os originaram: atributos gerais de dados nao diretamente mapeados no dicionario padrao. Amostra de colunas (ordem de leitura): [maintenance_id, maintenance_date, vessel_name, vessel_type, vessel_age_years, engine_type, port_name, maintenance_type].</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>VANET_5G_Energy_Transmission_Dataset.csv</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Bateria &amp; Sistema Eletrico (EV / Hibrido))</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Transmissao &amp; Troca de Marchas | Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (2.72 MB) estruturado com 62 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission_Power_mW, target_transmission_category); Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: Vehicle_Speed_kmph); Bateria &amp; Sistema Eletrico (EV / Hibrido) (colunas: Transmission_Power_mW, Receiving_Power_mW, Idle_Power_mW, Battery_Level_pct, Energy_Consumed_mJ); Navegacao, Rota &amp; Elevacao (GPS) (colunas: Vehicle_Direction_Change_deg, Inter_Vehicle_Distance_m, Route_Change_Count, Route_Stability_Index); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: Vehicle_ID). Amostra de colunas (ordem de leitura): [Vehicle_ID, RSU_ID, Road_Segment_ID, Time_Slot, Area_Type, Road_Type, Weather_Condition, Traffic_Density_Level].</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>VED_Static_Data_ICE&amp;HEV.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (XLSX)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Perfil de Veiculo &amp; Especificacoes Tecnicas)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Transmissao &amp; Troca de Marchas | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (0.02 MB) estruturado com 7 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: VehId, Generalized_Weight). Amostra de colunas (ordem de leitura): [VehId, Vehicle Type, Vehicle Class, Engine Configuration &amp; Displacement, Transmission, Drive Wheels, Generalized_Weight].</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>VED_Static_Data_PHEV&amp;EV.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (XLSX)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Perfil de Veiculo &amp; Especificacoes Tecnicas)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Transmissao &amp; Troca de Marchas | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (0.01 MB) estruturado com 7 colunas/variaveis. Temas detectados, com as colunas que os originaram: Transmissao &amp; Troca de Marchas (colunas: Transmission); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: VehId, Generalized_Weight). Amostra de colunas (ordem de leitura): [VehId, EngineType, Vehicle Class, Engine Configuration &amp; Displacement, Transmission, Drive Wheels, Generalized_Weight].</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>carbon_emissions_fleet_dataset.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (XLSX)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Navegacao, Rota &amp; Elevacao (GPS))</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Consumo de Combustivel &amp; Gases | Navegacao, Rota &amp; Elevacao (GPS) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (0.09 MB) estruturado com 9 colunas/variaveis. Temas detectados, com as colunas que os originaram: Consumo de Combustivel &amp; Gases (colunas: CO2_Emissions_g); Navegacao, Rota &amp; Elevacao (GPS) (colunas: Route_Type, Distance_km); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: Vehicle_ID). Amostra de colunas (ordem de leitura): [Vehicle_ID, Vehicle_Type, Route_Type, Delivery_Type, Distance_km, CO2_Emissions_g, On_Time_Delivery, Load_Utilization_%].</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>dataset.csv</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Navegacao, Rota &amp; Elevacao (GPS)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Navegacao, Rota &amp; Elevacao (GPS)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (2.78 MB) estruturado com 27 colunas/variaveis. Temas detectados, com as colunas que os originaram: Navegacao, Rota &amp; Elevacao (GPS) (colunas: LAT, LON). Amostra de colunas (ordem de leitura): [id, COND, LAT, LON, ALT, AX, AY, AZ].</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ev_charging_dataset.csv</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Bateria &amp; Sistema Eletrico (EV / Hibrido))</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS) | Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (20.94 MB) estruturado com 28 colunas/variaveis. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: Wind_Speed_m/s); Bateria &amp; Sistema Eletrico (EV / Hibrido) (colunas: Battery_Capacity_kWh, Energy_Consumption_Rate_kWh/km, Current_Latitude, Current_Longitude, Energy_Drawn_kWh); Navegacao, Rota &amp; Elevacao (GPS) (colunas: Current_Latitude, Current_Longitude, Destination_Latitude, Destination_Longitude, Distance_to_Destination_km); Gestao de Frota &amp; Viagens (Trip Logs) (colunas: Fleet_Size, Fleet_Schedule); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: Vehicle_ID). Amostra de colunas (ordem de leitura): [Date_Time, Vehicle_ID, Battery_Capacity_kWh, State_of_Charge_%, Energy_Consumption_Rate_kWh/km, Current_Latitude, Current_Longitude, Destination_Latitude].</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>fleet.csv</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Perfil de Veiculo &amp; Especificacoes Tecnicas)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (0.00 MB) estruturado com 5 colunas/variaveis. Temas detectados, com as colunas que os originaram: Gestao de Frota &amp; Viagens (Trip Logs) (colunas: fleet_test_id); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id, gross_vehicle_weight). Amostra de colunas (ordem de leitura): [vehicle_id, fleet_test_id, gross_vehicle_weight, total_mass_with_trailer, axle_class].</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>fleet_data.csv</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Navegacao, Rota &amp; Elevacao (GPS)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Navegacao, Rota &amp; Elevacao (GPS)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (1.02 MB) estruturado com 6 colunas/variaveis. Temas detectados, com as colunas que os originaram: Navegacao, Rota &amp; Elevacao (GPS) (colunas: Route_Optimization_Score). Amostra de colunas (ordem de leitura): [AI_Integration_Level, Fuel_Consumption_L, Downtime_Hours, Predicted_Maintenance_Accuracy, Route_Optimization_Score, Safety_Score].</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Pasta / Grupo</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Conjunto estruturado em pasta reunindo 1 arquivo(s) (totalizando 0.17 MB) e 3 variavel(is) unicas. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: speed). Amostra de colunas (ordem de leitura): [epoch, speed, hdop].</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>synthetic_telemetry_data.csv</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Powertrain &amp; Motor (RPM, Torque, Potencia))</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Powertrain &amp; Motor (RPM, Torque, Potencia) | Frenagem &amp; Pedais | Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Consumo de Combustivel &amp; Gases | Bateria &amp; Sistema Eletrico (EV / Hibrido) | Navegacao, Rota &amp; Elevacao (GPS) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (1.23 MB) estruturado com 41 colunas/variaveis. Temas detectados, com as colunas que os originaram: Powertrain &amp; Motor (RPM, Torque, Potencia) (colunas: engine_temp_c, engine_rpm, oil_pressure_psi, coolant_temp_c, engine_load_percent); Frenagem &amp; Pedais (colunas: brake_fluid_level_psi, brake_pad_wear_mm, brake_temp_c, brake_pedal_pos_percent, brake_issue_imminent); Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: wheel_speed_fl_kph, wheel_speed_fr_kph, wheel_speed_rl_kph, wheel_speed_rr_kph, vehicle_speed_kph); Consumo de Combustivel &amp; Gases (colunas: fuel_level_percent); Bateria &amp; Sistema Eletrico (EV / Hibrido) (colunas: battery_voltage_v, battery_current_a, battery_temp_c, battery_charge_percent, battery_health_percent); Navegacao, Rota &amp; Elevacao (GPS) (colunas: air_flow_rate_gps, gps_latitude, gps_longitude); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id, brand). Amostra de colunas (ordem de leitura): [vehicle_id, brand, timestamp, odometer_reading, engine_temp_c, engine_rpm, oil_pressure_psi, coolant_temp_c].</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>tracks.csv</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Arquivo (CSV)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="n">
         <v>15.62</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Misto (Dominante: Navegacao, Rota &amp; Elevacao (GPS))</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Navegacao, Rota &amp; Elevacao (GPS) | Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Arquivo de dados individual (15.62 MB) estruturado com 19 colunas/variaveis. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: avg_speed, max_speed); Navegacao, Rota &amp; Elevacao (GPS) (colunas: track_id, distance, track_gap); Gestao de Frota &amp; Viagens (Trip Logs) (colunas: start_time); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id). Amostra de colunas (ordem de leitura): [track_id, vehicle_id, tour_id, start_time, stop_time, distance, track_gap, avg_speed].</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>tracks.gf.csv</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo (CSV)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Misto (Dominante: Navegacao, Rota &amp; Elevacao (GPS))</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Dinamica Longitudinal (Velocidade &amp; Aceleracao X) | Navegacao, Rota &amp; Elevacao (GPS) | Gestao de Frota &amp; Viagens (Trip Logs) | Perfil de Veiculo &amp; Especificacoes Tecnicas</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Arquivo de dados individual (15.62 MB) estruturado com 19 colunas/variaveis. Temas detectados, com as colunas que os originaram: Dinamica Longitudinal (Velocidade &amp; Aceleracao X) (colunas: avg_speed, max_speed); Navegacao, Rota &amp; Elevacao (GPS) (colunas: track_id, distance, track_gap); Gestao de Frota &amp; Viagens (Trip Logs) (colunas: start_time); Perfil de Veiculo &amp; Especificacoes Tecnicas (colunas: vehicle_id). Amostra de colunas (ordem de leitura): [track_id, vehicle_id, tour_id, start_time, stop_time, distance, track_gap, avg_speed].</t>
         </is>
